--- a/toegestaan_gebruik.xlsx
+++ b/toegestaan_gebruik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delijn-my.sharepoint.com/personal/29076_delijn_be/Documents/vuilbak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{332F360B-EFCF-4E30-8AAC-6579376DFD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{332F360B-EFCF-4E30-8AAC-6579376DFD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5348E5D-4D80-4F1D-93D6-5B56CCDBAD35}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30696" windowHeight="17364" xr2:uid="{2F486639-FB36-4C94-8111-F3E3D3FA843B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>Naam</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Hoofd OT</t>
+  </si>
+  <si>
+    <t>paswoord_hash</t>
   </si>
 </sst>
 </file>
@@ -145,12 +148,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{844317D6-D12C-416C-B2C9-6737B89A18A2}" name="Tabel1" displayName="Tabel1" ref="A1:C12" totalsRowShown="0">
-  <autoFilter ref="A1:C12" xr:uid="{844317D6-D12C-416C-B2C9-6737B89A18A2}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{844317D6-D12C-416C-B2C9-6737B89A18A2}" name="Tabel1" displayName="Tabel1" ref="A1:D12" totalsRowShown="0">
+  <autoFilter ref="A1:D12" xr:uid="{844317D6-D12C-416C-B2C9-6737B89A18A2}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{C7BF91B6-D971-4F32-93B6-9654C0351B7E}" name="Naam"/>
     <tableColumn id="2" xr3:uid="{28CEC7D9-91C4-4716-841A-29953E589FD2}" name="Rol"/>
     <tableColumn id="3" xr3:uid="{E56461D6-A3D9-4B75-BB18-0E69A1AC8CAA}" name="paswoord"/>
+    <tableColumn id="4" xr3:uid="{6005815F-CBB8-4801-9B7B-82AF10776247}" name="paswoord_hash"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -473,14 +477,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6086A46-A0E2-420A-BEB9-E1BB161D6DD1}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -490,8 +494,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -502,7 +509,7 @@
         <v>29076</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -513,7 +520,7 @@
         <v>5579</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -524,7 +531,7 @@
         <v>4597</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -535,7 +542,7 @@
         <v>10170</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -546,7 +553,7 @@
         <v>15673</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -557,7 +564,7 @@
         <v>35348</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -568,7 +575,7 @@
         <v>7839</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -579,7 +586,7 @@
         <v>28740</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -590,7 +597,7 @@
         <v>35714</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -601,7 +608,7 @@
         <v>26268</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>

--- a/toegestaan_gebruik.xlsx
+++ b/toegestaan_gebruik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delijn-my.sharepoint.com/personal/29076_delijn_be/Documents/vuilbak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{332F360B-EFCF-4E30-8AAC-6579376DFD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5348E5D-4D80-4F1D-93D6-5B56CCDBAD35}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{332F360B-EFCF-4E30-8AAC-6579376DFD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDF2EA32-FC53-4B66-A8FB-C63D8C4C7430}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30696" windowHeight="17364" xr2:uid="{2F486639-FB36-4C94-8111-F3E3D3FA843B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>Naam</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Christoff</t>
   </si>
   <si>
-    <t>Teamcaoch</t>
-  </si>
-  <si>
     <t>ElsDW</t>
   </si>
   <si>
@@ -83,16 +80,10 @@
     <t>Sabrina</t>
   </si>
   <si>
-    <t>Teamleader</t>
-  </si>
-  <si>
-    <t>Assist-Operaties</t>
-  </si>
-  <si>
-    <t>Hoofd OT</t>
-  </si>
-  <si>
     <t>paswoord_hash</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
   </si>
 </sst>
 </file>
@@ -495,7 +486,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -503,7 +494,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>29076</v>
@@ -511,10 +502,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>5579</v>
@@ -522,10 +513,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>4597</v>
@@ -533,10 +524,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>10170</v>
@@ -544,10 +535,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>15673</v>
@@ -555,10 +546,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>35348</v>
@@ -566,10 +557,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>7839</v>
@@ -577,10 +568,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>28740</v>
@@ -588,7 +579,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -599,10 +590,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11">
         <v>26268</v>
@@ -610,10 +601,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12">
         <v>23897</v>
